--- a/AAII_Financials/Quarterly/CARR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CARR_QTR_FIN.xlsx
@@ -656,453 +656,466 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>6351000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5341000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4837000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5579000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6113000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5218000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5148000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5984000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5934000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5420000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4316000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4935000</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P8" s="3">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3">
         <v>5273000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5105000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5451000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5211000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4654000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5133000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5341000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5440000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4699000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4594000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5002000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3972000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3888000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4501000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4822000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4962000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4323000</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI8" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ8" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>4622000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4053000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3856000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4119000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4336000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3771000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3798000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4292000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4237000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3916000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3196000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3445000</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3">
         <v>3889000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3857000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3973000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3759000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3359000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3757000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3733000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3815000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3300000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3294000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3442000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2826000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2765000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3219000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3362000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3480000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3092000</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1729000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1288000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>981000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1460000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1777000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1447000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1350000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1692000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1697000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1504000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1120000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1490000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1384000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1248000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1478000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1452000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1295000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1376000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1608000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1625000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1399000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1300000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1560000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1146000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1123000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1282000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1460000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1482000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1231000</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1138,109 +1151,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E12" s="3">
         <v>143000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>160000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>151000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>161000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>153000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>162000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>172000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>160000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>192000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>138000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>126000</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3">
         <v>139000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>149000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>143000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>122000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>125000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>134000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>123000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>125000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>121000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>127000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>100000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>94000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>98000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>99000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>102000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>103000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>97000</v>
       </c>
-      <c r="AG12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1340,154 +1357,160 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E14" s="3">
         <v>122000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>41000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>63000</v>
       </c>
-      <c r="G14" s="3">
-        <v>49000</v>
-      </c>
       <c r="H14" s="3">
+        <v>46000</v>
+      </c>
+      <c r="I14" s="3">
         <v>14000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-354000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>75000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>162000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>253000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-191000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>305000</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>29000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>6000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>13000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>10000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>39000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>13000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>24000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>34000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>297000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-327000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>70000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>66000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>137000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>34000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>30000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>33000</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>314000</v>
+      </c>
+      <c r="E15" s="3">
         <v>315000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>329000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>325000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>317000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>303000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>318000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>312000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>294000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>308000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>123000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>95000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>137000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>136000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1542,8 +1565,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1576,210 +1602,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5521000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4990000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4744000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5046000</v>
       </c>
-      <c r="G17" s="3">
-        <v>5239000</v>
-      </c>
       <c r="H17" s="3">
+        <v>5242000</v>
+      </c>
+      <c r="I17" s="3">
         <v>4618000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4772000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5213000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5138000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4813000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4009000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4195000</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3">
         <v>4733000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4672000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3925000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4392000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2917000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4670000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4513000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4657000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4128000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3349000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3921000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3530000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3573000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3944000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4193000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4157000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3823000</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>830000</v>
+      </c>
+      <c r="E18" s="3">
         <v>351000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>93000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>533000</v>
       </c>
-      <c r="G18" s="3">
-        <v>874000</v>
-      </c>
       <c r="H18" s="3">
+        <v>871000</v>
+      </c>
+      <c r="I18" s="3">
         <v>600000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>376000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>771000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>796000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>607000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>307000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>740000</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3">
         <v>540000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>433000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1526000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>819000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1737000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>463000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>828000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>783000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>571000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1245000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1081000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>442000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>315000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>557000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>629000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>805000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>500000</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1815,79 +1848,80 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-58000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-31000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-47000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-60000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-78000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-44000</v>
       </c>
       <c r="I20" s="3">
         <v>-44000</v>
       </c>
       <c r="J20" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="K20" s="3">
         <v>-66000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-90000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-31000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-40000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-75000</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-44000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>20000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>15000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>6000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>38000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>14000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>16000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>23000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>21000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>16000</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>18000</v>
       </c>
       <c r="AA20" s="3">
         <v>18000</v>
@@ -1896,432 +1930,447 @@
         <v>18000</v>
       </c>
       <c r="AC20" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AD20" s="3">
         <v>34000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>70000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>63000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>69000</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1202000</v>
+      </c>
+      <c r="E21" s="3">
         <v>697000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>469000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>918000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1269000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1266000</v>
+      </c>
+      <c r="I21" s="3">
         <v>947000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>738000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1149000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1180000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>946000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>470000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>910000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>137000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>720000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>576000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1643000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>901000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1854000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>564000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>927000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>891000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>675000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1356000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1181000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>538000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>414000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>675000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>783000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>950000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>654000</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>126000</v>
+      </c>
+      <c r="E22" s="3">
         <v>111000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>115000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>116000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>115000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>112000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>118000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>131000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>175000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>156000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>97000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>73000</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3">
         <v>71000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>76000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>71000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>68000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>87000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>72000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>76000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>75000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>96000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>85000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>90000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>85000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>38000</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE22" s="3">
         <v>20000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>9000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>26000</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI22" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ22" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>721000</v>
+      </c>
+      <c r="E23" s="3">
         <v>170000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>433000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>812000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>548000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>693000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>770000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>567000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>244000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>504000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>471000</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3">
         <v>509000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>377000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1470000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>757000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1688000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>405000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>768000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>731000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>496000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1176000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1009000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>375000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>295000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>591000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>679000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>859000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>543000</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-96000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-32000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>162000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>111000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>723000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>172000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>120000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>47000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>68000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>177000</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3">
         <v>122000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>99000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>138000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>170000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>301000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>73000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>288000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>234000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>104000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>289000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>261000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>106000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>193000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>137000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>175000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>65000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>140000</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2421,210 +2470,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>541000</v>
+      </c>
+      <c r="E26" s="3">
         <v>266000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>37000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>434000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>650000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>437000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-30000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>598000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>447000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>197000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>436000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>294000</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3">
         <v>387000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>278000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1332000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>587000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1387000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>332000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>480000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>497000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>392000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>887000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>748000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>269000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>102000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>454000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>504000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>794000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>403000</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>501000</v>
+      </c>
+      <c r="E27" s="3">
         <v>238000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>53000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>428000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>591000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>412000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2551000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>447000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2337000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>269000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>420000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>357000</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3">
         <v>373000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>270000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1312000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>573000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1379000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>324000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>469000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>487000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>384000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>884000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>741000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>261000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>96000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>440000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>492000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>784000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>400000</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2724,47 +2782,50 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>-1000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>25000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>21000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-17000</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>2599000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-117000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>1922000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>92000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>3000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>87000</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
@@ -2825,8 +2886,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2926,8 +2990,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3027,79 +3094,82 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E32" s="3">
         <v>31000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>47000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>60000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>78000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>44000</v>
       </c>
       <c r="I32" s="3">
         <v>44000</v>
       </c>
       <c r="J32" s="3">
+        <v>44000</v>
+      </c>
+      <c r="K32" s="3">
         <v>66000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>90000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>31000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>40000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>75000</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
         <v>44000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-20000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-15000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-6000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-38000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-14000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-16000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-23000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-16000</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-18000</v>
       </c>
       <c r="AA32" s="3">
         <v>-18000</v>
@@ -3108,129 +3178,135 @@
         <v>-18000</v>
       </c>
       <c r="AC32" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-70000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-63000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-69000</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>501000</v>
+      </c>
+      <c r="E33" s="3">
         <v>238000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>53000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>428000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>591000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>412000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2551000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>447000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2337000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>269000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>420000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>357000</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3">
         <v>373000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>270000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1312000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>573000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1379000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>324000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>469000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>487000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>384000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>884000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>741000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>261000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>96000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>440000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>492000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>784000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>400000</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3330,215 +3406,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>501000</v>
+      </c>
+      <c r="E35" s="3">
         <v>238000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>53000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>428000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>591000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>412000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2551000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>447000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2337000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>269000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>420000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>357000</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3">
         <v>373000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>270000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1312000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>573000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1379000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>324000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>469000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>487000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>384000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>884000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>741000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>261000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>96000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>440000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>492000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>784000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>400000</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3574,8 +3659,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3611,89 +3697,90 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1344000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1371000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1555000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1423000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1797000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1698000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3969000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2225000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2919000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1313000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9852000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3902000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3209000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3347000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3520000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2985000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3017000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3604000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2987000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2671000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2630000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2599000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3115000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3848000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2704000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>768000</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3712,8 +3799,11 @@
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3813,89 +3903,92 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3702000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3663000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3138000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3655000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3854000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3438000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3017000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3100000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3525000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3481000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2386000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3635000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3790000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3600000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3370000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3669000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3535000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3254000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2906000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3171000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3823000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3525000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3437000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3625000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3426000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3325000</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3914,89 +4007,92 @@
       <c r="AI43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2759000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2581000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2483000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3004000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2888000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2648000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2299000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2646000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3045000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3189000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1823000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2562000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2699000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2803000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2640000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2664000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2350000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2358000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1970000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1926000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1885000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1854000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1629000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1581000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1639000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1556000</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4015,89 +4111,92 @@
       <c r="AI44" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ44" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1609000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1403000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1355000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>757000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>592000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>660000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>603000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3209000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2084000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3732000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5514000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>412000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>443000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>408000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>349000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>422000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>374000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>386000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3544000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3532000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>416000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>350000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>343000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>280000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>284000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>319000</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4116,89 +4215,92 @@
       <c r="AI45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9414000</v>
+      </c>
+      <c r="E46" s="3">
         <v>9018000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8533000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8839000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9131000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8444000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9891000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11194000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11573000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11715000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>19576000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10511000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10141000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10158000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9879000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9740000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9276000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9602000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11407000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11300000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8754000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>8328000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8524000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>9334000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8053000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5968000</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,89 +4319,92 @@
       <c r="AI46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1341000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1331000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1321000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1381000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1353000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1253000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1194000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1287000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1221000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1155000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1140000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1166000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1139000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1103000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1766000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1777000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2243000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2170000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2226000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2194000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2199000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2128000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2060000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2210000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2925000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2208000</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4318,89 +4423,92 @@
       <c r="AI47" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ47" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3730000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3673000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3711000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3772000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3757000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3603000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3553000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3583000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3752000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3812000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2581000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2787000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2862000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2902000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2883000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2680000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2400000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2421000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2466000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2390000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2623000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2547000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2598000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2499000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2494000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2503000</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4419,89 +4527,92 @@
       <c r="AI48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>21023000</v>
+      </c>
+      <c r="E49" s="3">
         <v>21300000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>21827000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22240000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>22442000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>21439000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>21033000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22412000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22293000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>22717000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8465000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10925000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11108000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11274000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11319000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10930000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9525000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9776000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9858000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9718000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>11350000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>11079000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>11176000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>10930000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>10759000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>10662000</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4520,8 +4631,11 @@
       <c r="AI49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4621,8 +4735,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4722,89 +4839,92 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>724000</v>
+      </c>
+      <c r="E52" s="3">
         <v>648000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>641000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>591000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>543000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>524000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>536000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>528000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>606000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>558000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>316000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>425000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>336000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>329000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>239000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>223000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>218000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>224000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>215000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>186000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>812000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>786000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>735000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>755000</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC52" s="3">
         <v>660000</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +4943,11 @@
       <c r="AI52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4924,89 +5047,92 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37372000</v>
+      </c>
+      <c r="E54" s="3">
         <v>37186000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>37190000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>38077000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>38493000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36447000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>37403000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>40201000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>40424000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>40810000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32822000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>26544000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>26284000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26411000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26086000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>25350000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>23662000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>24193000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>26172000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>25788000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>25738000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>24868000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>25093000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>25728000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>24176000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>22001000</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5025,8 +5151,11 @@
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5062,8 +5191,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5099,89 +5229,90 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3216000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2979000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2702000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2959000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3214000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3015000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2458000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2829000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3181000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3074000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2483000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2887000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2956000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2926000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2833000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2817000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2403000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2519000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2334000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2158000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2362000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2175000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1936000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2019000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1765000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1776000</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5200,89 +5331,92 @@
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1638000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1736000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>610000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>580000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>107000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>104000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1471000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2095000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2052000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1248000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>144000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>134000</v>
       </c>
       <c r="O58" s="3">
         <v>134000</v>
       </c>
       <c r="P58" s="3">
+        <v>134000</v>
+      </c>
+      <c r="Q58" s="3">
         <v>142000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>140000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>219000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>269000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>256000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>183000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>130000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>125000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>153000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>191000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>223000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>301000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>218000</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5301,89 +5435,92 @@
       <c r="AI58" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1358000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1010000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>980000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>746000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>642000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>615000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>639000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1440000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1253000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1387000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1925000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>631000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>781000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>687000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3059000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2977000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2874000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2756000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4110000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3780000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3117000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2810000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2983000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2940000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2723000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2457000</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5402,89 +5539,92 @@
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9231000</v>
+      </c>
+      <c r="E60" s="3">
         <v>8585000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7114000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7747000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7829000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7011000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7892000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10378000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10675000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8637000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6981000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6349000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6234000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5958000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6032000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6013000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5546000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5531000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6627000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6068000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5604000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5138000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5110000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5182000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4789000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4451000</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5503,89 +5643,92 @@
       <c r="AI60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10756000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10837000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11783000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11760000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11780000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11517000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11458000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10782000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11771000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>16152000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14575000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9116000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9140000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9214000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8702000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8670000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8298000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8305000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9513000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9558000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9600000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9577000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>10036000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>11751000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>11728000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>11029000</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -5604,89 +5747,92 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1889000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1879000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1937000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1382000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1384000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1307000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1265000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1387000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1307000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1427000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1429000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1521000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1542000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1662000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3276000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3204000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2826000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2927000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2938000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2940000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3414000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3335000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3369000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3358000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3293000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3495000</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5705,8 +5851,11 @@
       <c r="AI62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5806,8 +5955,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5907,8 +6059,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6008,89 +6163,92 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23900000</v>
+      </c>
+      <c r="E66" s="3">
         <v>23385000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23062000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23238000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>23479000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>22249000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>23008000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25159000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>26345000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>28904000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>23817000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18042000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17996000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>17943000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18328000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>18198000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16966000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>17092000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19405000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>18888000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>18982000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>18379000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>18841000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>20632000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>20148000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19304000</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6109,8 +6267,11 @@
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6146,8 +6307,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6247,8 +6409,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6348,8 +6513,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6449,8 +6617,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6550,86 +6721,89 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12536000</v>
+      </c>
+      <c r="E72" s="3">
         <v>12431000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>12193000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12530000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12294000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11895000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11483000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9301000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8854000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6860000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6591000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6486000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6129000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6239000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5866000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5876000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4564000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4244000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2865000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2774000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2305000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2027000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1643000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>932000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>191000</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6645,14 +6819,17 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AH72" s="3">
-        <v>0</v>
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AI72" s="3">
         <v>0</v>
       </c>
+      <c r="AJ72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6752,8 +6929,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6853,8 +7033,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6954,89 +7137,92 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13147000</v>
+      </c>
+      <c r="E76" s="3">
         <v>13452000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13804000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14509000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14706000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13859000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14081000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14693000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13768000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11561000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8677000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8184000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7969000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8134000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7758000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7152000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6696000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7101000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6767000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6900000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6756000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6489000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6252000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5096000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4028000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2697000</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7055,8 +7241,11 @@
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7156,215 +7345,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>501000</v>
+      </c>
+      <c r="E81" s="3">
         <v>238000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>53000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>428000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>591000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>412000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2551000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>447000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2337000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>269000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>420000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>357000</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3">
         <v>373000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>270000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1312000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>573000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1379000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>324000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>469000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>487000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>384000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>884000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>741000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>261000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>96000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>440000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>492000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>784000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>400000</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7400,109 +7598,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E83" s="3">
         <v>95000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>107000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>99000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>86000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>97000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>69000</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
         <v>72000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>78000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>64000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>56000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>58000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>123000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>102000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>76000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>79000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>87000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>83000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>85000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>83000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>95000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>82000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>78000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>81000</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>84000</v>
       </c>
       <c r="AD83" s="3">
         <v>84000</v>
       </c>
       <c r="AE83" s="3">
+        <v>84000</v>
+      </c>
+      <c r="AF83" s="3">
         <v>82000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>85000</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7602,8 +7804,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7703,8 +7908,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7804,8 +8012,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7905,8 +8116,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8006,109 +8220,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>927000</v>
+      </c>
+      <c r="E89" s="3">
         <v>79000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1040000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>341000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>649000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>483000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>132000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-269000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>660000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>40000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1062000</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>120000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1123000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>790000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>32000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-202000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>913000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>579000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>561000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>184000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>199000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>937000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>509000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>47000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1013000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>618000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>554000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-183000</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8144,109 +8364,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-117000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-94000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-131000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-117000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-81000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-63000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-217000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-92000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-108000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-102000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-222000</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-70000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-140000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-91000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-66000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-56000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-138000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-74000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-79000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-53000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-161000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-57000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-48000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-104000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-50000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-48000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-41000</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8346,8 +8570,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8447,109 +8674,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-170000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-65000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-110000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-119000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-55000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-23000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3089000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1159000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>4808000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11081000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-229000</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-300000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-600000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-175000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>2820000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-266000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-125000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-252000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-49000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>876000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>333000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>25000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-128000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-63000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-70000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-37000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-43000</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8585,80 +8818,81 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>199000</v>
+      </c>
+      <c r="E96" s="3">
         <v>201000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>189000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>193000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>192000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>198000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>156000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>184000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>171000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>159000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>155000</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q96" s="3">
         <v>154000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-125000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-127000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-128000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-129000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-104000</v>
       </c>
       <c r="V96" s="3">
         <v>-104000</v>
       </c>
       <c r="W96" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-105000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-104000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-68000</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -8686,8 +8920,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8787,8 +9024,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8888,8 +9128,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8989,307 +9232,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-760000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-141000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-787000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-591000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-547000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2747000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1686000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1544000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3785000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2379000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5300000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-213000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-347000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-150000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-414000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2020000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-337000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-327000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-255000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-643000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1854000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-142000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1391000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-76000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-872000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-603000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-435000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-57000</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E101" s="3">
         <v>17000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-85000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>64000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-14000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-68000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>133000</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
         <v>20000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>59000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-74000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-40000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>59000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-74000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-40000</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-1000</v>
       </c>
       <c r="U101" s="3">
         <v>-1000</v>
       </c>
       <c r="V101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="W101" s="3">
         <v>-13000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>7000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>45000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>17000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>11000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-28000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>13000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>16000</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI101" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ101" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-140000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>156000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-374000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>98000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2270000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1450000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-590000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1669000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8730000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6266000</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-173000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>535000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-34000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-597000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>597000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>309000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>114000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>61000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-517000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-734000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1145000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1936000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-185000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>91000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>73000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-267000</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
